--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -26,8 +26,11 @@
     <sheet name="SERIES" sheetId="17" state="visible" r:id="rId17"/>
     <sheet name="CLUBS" sheetId="18" state="visible" r:id="rId18"/>
     <sheet name="META" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$4</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -35,7 +38,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -50,8 +53,12 @@
       <name val="Arial"/>
       <b val="1"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -73,6 +80,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00305496"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -86,12 +98,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -15842,7 +15860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D2"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15886,6 +15904,52 @@
       <c r="D2" t="inlineStr">
         <is>
           <t>DS-PDF</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id: CLUB_S1981_82_0213 'RH Sušice' prev→CLUB_S1980_81_0206 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0016</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1981_82_0016 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1981_82_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0017</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>[TBD] pyramida: SYSTEM NODE_S1981_82_0017 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1981_82_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
         </is>
       </c>
     </row>
@@ -49586,6 +49650,127 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+    <col width="88" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>typ</t>
+        </is>
+      </c>
+      <c r="C1" s="5" t="inlineStr">
+        <is>
+          <t>reference</t>
+        </is>
+      </c>
+      <c r="D1" s="5" t="inlineStr">
+        <is>
+          <t>popis</t>
+        </is>
+      </c>
+      <c r="E1" s="5" t="inlineStr">
+        <is>
+          <t>vyřešeno? (ANO/ne)</t>
+        </is>
+      </c>
+      <c r="F1" s="5" t="inlineStr">
+        <is>
+          <t>poznámka kolegy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>prev_club_id</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0213</t>
+        </is>
+      </c>
+      <c r="D2" s="6" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0213 'RH Sušice' prev→CLUB_S1980_81_0206 jen dle jména (město liší) — ověřit (D24)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0016</t>
+        </is>
+      </c>
+      <c r="D3" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1981_82_0016 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1981_82_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>pyramida</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0017</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>SYSTEM NODE_S1981_82_0017 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1981_82_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:F4"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$50</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15860,7 +15860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15910,7 +15910,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id: CLUB_S1981_82_0213 'RH Sušice' prev→CLUB_S1980_81_0206 jen dle jména (město liší) — ověřit (D24)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -15920,14 +15920,9 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NODE_S1981_82_0016</t>
-        </is>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1981_82_0016 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1981_82_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15937,17 +15932,564 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NODE_S1981_82_0017</t>
-        </is>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] pyramida: SYSTEM NODE_S1981_82_0017 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1981_82_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1980_81_0206 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -22314,12 +22856,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Plzeň</t>
+          <t>České Budějovice</t>
         </is>
       </c>
     </row>
@@ -22655,12 +23197,12 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem.</t>
+          <t>Ústí nad Labem = TJ Slovan NV Ústí nL Labem (Wiki D42 - registr ustavy 04/2026). **NV** = Národní výbor (správní orgán). city Ústí nad Labem. || TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>NV Ústí nad Labem</t>
+          <t>Ústí nad Labem</t>
         </is>
       </c>
     </row>
@@ -22739,12 +23281,12 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha.</t>
+          <t>Praha = TJ DP I. ČLTK Praha (Wiki D42 - registr ustavy 04/2026). I.ČLTK = I. Český Lawn Tennis Club Praha (1893). DP = Dopravní podnik. city Praha. || TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>DP I. ČLTK Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -22996,12 +23538,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha.</t>
+          <t>Praha = TJ Uhelné sklady Praha (Wiki D42 - registr ustavy 04/2026). **Uhelné sklady** = podnik na distribuci uhli. city Praha. || TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Uhelné sklady Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -23169,12 +23711,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Hradec Králové</t>
         </is>
       </c>
     </row>
@@ -23342,12 +23884,12 @@
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec.</t>
+          <t>Třinec = TJ TŽ VŘSR Třinec (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj. **TŽ** = Třinecké železárny. **VŘSR** = Velka řijnova socialisticka revoluce (pojmenovani po vyroci VŘSR 1917). city Třinec. || TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>TŽ VŘSR Třinec</t>
+          <t>Třinec</t>
         </is>
       </c>
     </row>
@@ -23384,12 +23926,12 @@
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou.</t>
+          <t>Žďár nL Sázavou = TJ Žďas Žďár nL Sázavou (Wiki D42 - registr ustavy 04/2026). Vysocina/Jihlavsky kraj. **ŽĎAS** = Žďárské strojírny a slévárny (kovaci/lisovaci stroje). 'Žďas' = lokalní pravopis. city Žďár nad Sázavou. || TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Žďas Žďár nad Sázavou</t>
+          <t>Žďár nad Sázavou</t>
         </is>
       </c>
     </row>
@@ -23426,12 +23968,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Chomutov</t>
+          <t>Mladá Boleslav</t>
         </is>
       </c>
     </row>
@@ -23557,12 +24099,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>ČSA Karviná</t>
         </is>
       </c>
     </row>
@@ -23735,12 +24277,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Kolora Liberec</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -23819,12 +24361,12 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom.</t>
+          <t>Dubnica nad Váhom = TJ SMZ Spartak Dubnica nad Váhom (Wiki D42 - registr ustavy 04/2026). Slovensky/Trencianky kraj. SMZ = Stredoslovenske strojirenske zavody. city Dubnica nad Váhom. || TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>SMZ Dubnica nad Váhom</t>
+          <t>Dubnica nad Váhom</t>
         </is>
       </c>
     </row>
@@ -23987,12 +24529,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves.</t>
+          <t>DSO Lokomotíva Spišská Nová Ves (Oblastní sk. B). Oprava clean: chybi diakritika ("Spišska" → "Spišská", "Nova" → "Nová"). prev 54/55 0810 (TJ Lokomotíva Spišská Nová Ves). || Spišská Nová Ves = HK Spišská Nová Ves (Wiki - registr ustavy 04/2026). Slovensky kraj. city Spišská Nová Ves. || TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Spišská Nová Ves</t>
+          <t>Nová Ves</t>
         </is>
       </c>
     </row>
@@ -24298,12 +24840,12 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov.</t>
+          <t>Vyškov = TJ VTJ VVŠ PV Vyškov (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj. **VVŠ PV** = Vysoká vojenská škola pozemního vojska Vyškov. **VTJ** = Vojenská telovychovna jednota. city Vyškov. || TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>VVŠ PV Vyškov</t>
+          <t>Vyškov</t>
         </is>
       </c>
     </row>
@@ -24708,12 +25250,12 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Praha-Žižkov = TJ Rudá Hvězda Žižkov (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 3. RH = Ruda hvezda (SNB). city Praha (Žižkov).</t>
+          <t>Praha-Žižkov = TJ Rudá Hvězda Žižkov (Wiki D42 - registr ustavy 04/2026). Mestska cast Praha 3. RH = Ruda hvezda (SNB). city Praha (Žižkov). || TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>Rudá Hvězda Žižkov</t>
+          <t>Rudá Hvězda</t>
         </is>
       </c>
     </row>
@@ -24960,12 +25502,12 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Praha = TJ UDPM JF Praha (Wiki D42 - registr ustavy 04/2026). **UDPM** = Ústřední dům pionýrů a mládeže, **JF** = Julia Fučíka (pojmenovani). Studentsky/mladez klub. city Praha.</t>
+          <t>Praha = TJ UDPM JF Praha (Wiki D42 - registr ustavy 04/2026). **UDPM** = Ústřední dům pionýrů a mládeže, **JF** = Julia Fučíka (pojmenovani). Studentsky/mladez klub. city Praha. || TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>UDPM JF Praha</t>
+          <t>Praha</t>
         </is>
       </c>
     </row>
@@ -25044,12 +25586,12 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Plzeň-Černice = TJ Sokol Černice (Wiki D42 - registr ustavy 04/2026). Plzensky/Zapadocesky kraj. Mestska cast Plzně. city Plzeň (Černice).</t>
+          <t>Plzeň-Černice = TJ Sokol Černice (Wiki D42 - registr ustavy 04/2026). Plzensky/Zapadocesky kraj. Mestska cast Plzně. city Plzeň (Černice). || TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>Černice</t>
+          <t>Horní Počernice</t>
         </is>
       </c>
     </row>
@@ -26460,12 +27002,12 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -27862,12 +28404,12 @@
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -27904,12 +28446,12 @@
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr.</t>
+          <t>Králův Dvůr = TJ KŽ Králův Dvůr (Wiki D42 - registr ustavy 04/2026). Stredocesky kraj (okres Beroun). **KŽ** = Kralovedvorske železárny (Železárny Králův Dvůr - historicky podnik). city Králův Dvůr. || TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
         <is>
-          <t>KŽ Králův Dvůr</t>
+          <t>Králův Dvůr</t>
         </is>
       </c>
     </row>
@@ -27988,12 +28530,12 @@
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J139" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -28245,12 +28787,12 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou.</t>
+          <t>Hluboká nL Vltavou = Tatran Hluboká nL Vltavou (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Ceske Budejovice). city Hluboká nad Vltavou. || TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J145" t="inlineStr">
         <is>
-          <t>Hluboká</t>
+          <t>Hluboká nad Vltavou</t>
         </is>
       </c>
     </row>
@@ -28329,12 +28871,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou.</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Lokomotiva  Veselí nad Moravou</t>
+          <t>Veselí nad Lužnicí</t>
         </is>
       </c>
     </row>
@@ -28910,12 +29452,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá.</t>
+          <t>Horní Planá = TJ Smrčina Horní Planá (Wiki D42 - registr ustavy 04/2026). Jihocesky kraj (okres Český Krumlov). **Smrčina** = pojmenovani po horach Smrciny. city Horní Planá. || TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>Smrčina Horní Planá</t>
+          <t>Planá</t>
         </is>
       </c>
     </row>
@@ -29328,12 +29870,12 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec.</t>
+          <t>Slovan JH = HC Vajgar/Strelci JH (Wiki D42 - registr ustavy 04/2026). Chain VBK Vajgar (1929). NE Hradec Kralove. city Jindřichův Hradec. || TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>Vajgar Jindřichův Hradec</t>
+          <t>Jindřichův Hradec</t>
         </is>
       </c>
     </row>
@@ -31828,12 +32370,12 @@
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu.</t>
+          <t>Luby u Chebu = TJ Start VD Luby (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj (okres Cheb). **Luby u Chebu** = svetove znamy vyrobce hudebnich nastroju (Cremona Luby - housle/kytary). 'VD' = vyrobni druzstvo. NE Luby u Klatov. city Luby u Chebu. || TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>Start VD Luby</t>
+          <t>Luby</t>
         </is>
       </c>
     </row>
@@ -32006,12 +32548,12 @@
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb.</t>
+          <t>Cheb = TJ Lokomotiva depo Cheb (Wiki D42 - registr ustavy 04/2026). Karlovarsky kraj. **Lokomotivni depo Cheb** = železničárský klub (drive vyznamne pohranicni depo, nejdulezitejsi prepojeni s NSR). city Cheb. || TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>Lokomotiva depo Cheb</t>
+          <t>Cheb</t>
         </is>
       </c>
     </row>
@@ -32918,12 +33460,12 @@
       </c>
       <c r="I249" t="inlineStr">
         <is>
-          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín.</t>
+          <t>Děčín = TJ Technické služby Děčín (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Technické služby** = mestske podnik (cisteni, odpady). city Děčín. || TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J249" t="inlineStr">
         <is>
-          <t>Technické služby Děčín</t>
+          <t>Děčín</t>
         </is>
       </c>
     </row>
@@ -33857,12 +34399,12 @@
       </c>
       <c r="I271" t="inlineStr">
         <is>
-          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov.</t>
+          <t>Chomutov = TJ Důl Jana Žižky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **Důl Jana Žižky** = hnedouhelny dul Chomutovska. city Chomutov. || TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J271" t="inlineStr">
         <is>
-          <t>Důl Jana Žižky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -34008,12 +34550,12 @@
       </c>
       <c r="I274" t="inlineStr">
         <is>
-          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov.</t>
+          <t>Chomutov = TJ SSM Statky Chomutov (Wiki D42 - registr ustavy 04/2026). Severocesky/Ustecky kraj. **SSM Statky** = Socialistický svaz mládeže (oddil drevorubeckych/zemedelskych statku). city Chomutov. || TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J274" t="inlineStr">
         <is>
-          <t>SSM Statky Chomutov</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -34663,12 +35205,12 @@
       </c>
       <c r="I289" t="inlineStr">
         <is>
-          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov.</t>
+          <t>Hronov = TJ Tepna ČKD Hronov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Náchod). **Tepna ČKD Hronov** = textilni + strojirensky podnik (slouceny Tepna Náchod + ČKD pobocka). NE Hronovce (SVK)! city Hronov. || TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J289" t="inlineStr">
         <is>
-          <t>Tepna ČKD Hronov</t>
+          <t>Hronov</t>
         </is>
       </c>
     </row>
@@ -35125,12 +35667,12 @@
       </c>
       <c r="I300" t="inlineStr">
         <is>
-          <t>Nový Bydžov = TJ OSP Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). **OSP** = Okresní stavební podnik. city Nový Bydžov.</t>
+          <t>Nový Bydžov = TJ OSP Nový Bydžov (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Kralovehradecky kraj (okres Hradec Kralove). **OSP** = Okresní stavební podnik. city Nový Bydžov. || TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J300" t="inlineStr">
         <is>
-          <t>OSP Nový Bydžov</t>
+          <t>Nový Bydžov</t>
         </is>
       </c>
     </row>
@@ -36547,12 +37089,12 @@
       </c>
       <c r="I331" t="inlineStr">
         <is>
-          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice.</t>
+          <t>Pardubice = TJ SSM SNV Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **SSM** = Socialistický svaz mládeže, **SNV** = pravdepodobne 'Sbor narodni bezpecnosti' (= SNB - policejni klub). city Pardubice. || TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J331" t="inlineStr">
         <is>
-          <t>SSM SNV Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -36594,12 +37136,12 @@
       </c>
       <c r="I332" t="inlineStr">
         <is>
-          <t>Pardubice = TJ Povodí Labe Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Povodí Labe** = státní podnik (správa labské vodní cesty). city Pardubice.</t>
+          <t>Pardubice = TJ Povodí Labe Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Povodí Labe** = státní podnik (správa labské vodní cesty). city Pardubice. || TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J332" t="inlineStr">
         <is>
-          <t>Povodí Labe Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -37012,12 +37554,12 @@
       </c>
       <c r="I341" t="inlineStr">
         <is>
-          <t>Pardubice = TJ Dopravní podnik Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Dopravní podnik** = mestske dopravce (MHD - autobusy, trolejbusy). city Pardubice.</t>
+          <t>Pardubice = TJ Dopravní podnik Pardubice (Wiki D42 - registr ustavy 04/2026). Vychodocesky/Pardubicky kraj. **Dopravní podnik** = mestske dopravce (MHD - autobusy, trolejbusy). city Pardubice. || TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J341" t="inlineStr">
         <is>
-          <t>Dopravní podnik Pardubice</t>
+          <t>Pardubice</t>
         </is>
       </c>
     </row>
@@ -38837,12 +39379,12 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>Olomouc</t>
+          <t>Modeta Jihlava</t>
         </is>
       </c>
     </row>
@@ -41662,12 +42204,12 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Voděrady</t>
+          <t>Horní Benešov</t>
         </is>
       </c>
     </row>
@@ -42040,12 +42582,12 @@
       </c>
       <c r="I455" t="inlineStr">
         <is>
-          <t>Horní Suchá = TJ Důl Prezident Gottwald Horní Suchá (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina, district '(KAR)' potvrzen). **Důl Prezident Gottwald** = velky uhelny dul Ostravsko-karvinske panvi (pojmenovani po prezidentovi Klementu Gottwaldovi). city Horní Suchá.</t>
+          <t>Horní Suchá = TJ Důl Prezident Gottwald Horní Suchá (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Moravskoslezsky kraj (okres Karvina, district '(KAR)' potvrzen). **Důl Prezident Gottwald** = velky uhelny dul Ostravsko-karvinske panvi (pojmenovani po prezidentovi Klementu Gottwaldovi). city Horní Suchá. || TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J455" t="inlineStr">
         <is>
-          <t>Důl Prezident Gottwald Horní Suchá</t>
+          <t>Horní Suchá</t>
         </is>
       </c>
     </row>
@@ -42260,12 +42802,12 @@
       </c>
       <c r="I460" t="inlineStr">
         <is>
-          <t>Olomouc = TJ Sigma ZTS Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Stejne jako ZTS Sigma - jiny poradi slov. city Olomouc.</t>
+          <t>Olomouc = TJ Sigma ZTS Olomouc (Wiki D42 - registr ustavy 04/2026). Severomoravsky/Olomoucky kraj. Stejne jako ZTS Sigma - jiny poradi slov. city Olomouc. || TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J460" t="inlineStr">
         <is>
-          <t>Sigma ZTS Olomouc</t>
+          <t>Olomouc</t>
         </is>
       </c>
     </row>
@@ -49656,11 +50198,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F4"/>
+  <dimension ref="A1:F50"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
     <col width="26" customWidth="1" min="3" max="3"/>
     <col width="88" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
@@ -49705,21 +50247,19 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>prev_club_id</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0213</t>
+          <t>CLUB_S1981_82_0006</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0213 'RH Sušice' prev→CLUB_S1980_81_0206 jen dle jména (město liší) — ověřit (D24)</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
+          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -49727,21 +50267,19 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>NODE_S1981_82_0016</t>
+          <t>CLUB_S1981_82_0014</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1981_82_0016 'Kvalifikace o ČNHL - skupina A' (L25, parent=NODE_S1981_82_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -49749,24 +50287,942 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>pyramida</t>
+          <t>prev_club_id / identita</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>NODE_S1981_82_0017</t>
+          <t>CLUB_S1981_82_0016</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>SYSTEM NODE_S1981_82_0017 'Kvalifikace o ČNHL - skupina B' (L25, parent=NODE_S1981_82_0015) vnořená baráž — feeds_into ponecháno prázdné (ověřit cíl ručně)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0022</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0026</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0030</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0031</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0032</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0035</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0039</t>
+        </is>
+      </c>
+      <c r="D11" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0041</t>
+        </is>
+      </c>
+      <c r="D12" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0045</t>
+        </is>
+      </c>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0053</t>
+        </is>
+      </c>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0068</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0068</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0074</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0076</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0110</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0141</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0142</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0145</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0151</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0153</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0153</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0166</t>
+        </is>
+      </c>
+      <c r="D26" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0175</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0187</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0213</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1980_81_0206 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0230</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0234</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0256</t>
+        </is>
+      </c>
+      <c r="D32" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0269</t>
+        </is>
+      </c>
+      <c r="D33" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0278</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0281</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0290</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0294</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0297</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0308</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0310</t>
+        </is>
+      </c>
+      <c r="D40" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0339</t>
+        </is>
+      </c>
+      <c r="D41" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0340</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0349</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0385</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0390</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0416</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0419</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0456</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0465</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>CLUB_S1981_82_0470</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F4"/>
+  <autoFilter ref="A1:F50"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$50</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$42</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15860,7 +15860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15910,7 +15910,7 @@
     <row r="3">
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -15922,7 +15922,7 @@
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15934,7 +15934,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15946,7 +15946,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15958,7 +15958,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15970,7 +15970,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15982,7 +15982,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15994,7 +15994,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -16006,7 +16006,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -16018,7 +16018,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -16030,7 +16030,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -16042,7 +16042,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -16054,7 +16054,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -16066,7 +16066,7 @@
     <row r="16">
       <c r="C16" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -16078,7 +16078,7 @@
     <row r="17">
       <c r="C17" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -16090,7 +16090,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -16102,7 +16102,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -16114,7 +16114,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -16126,7 +16126,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -16138,7 +16138,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -16150,7 +16150,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -16162,7 +16162,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1980_81_0206 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -16174,7 +16174,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -16186,7 +16186,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -16198,7 +16198,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -16210,7 +16210,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -16222,7 +16222,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -16234,7 +16234,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1980_81_0206 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -16246,7 +16246,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -16258,7 +16258,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -16270,7 +16270,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -16282,7 +16282,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -16294,7 +16294,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -16306,7 +16306,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -16318,7 +16318,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -16330,7 +16330,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -16342,7 +16342,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -16354,7 +16354,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -16366,7 +16366,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -16378,7 +16378,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -16390,106 +16390,10 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -16506,7 +16410,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K102"/>
+  <dimension ref="A1:L102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16565,6 +16469,11 @@
           <t>note</t>
         </is>
       </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>prev_node_id</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -16607,6 +16516,11 @@
           <t>12 týmů, 4kolově, bez remíz (W/WOT/LOT/L). Mistr: Dukla Jihlava.</t>
         </is>
       </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0001</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -16654,6 +16568,11 @@
           <t>Přerov - Slovan CHZJD Bratislava 0:3. 1. a 3. utkání doma; případné 5. utkání v Trenčíně. Při nerozhodném výsledku 3x 5 minut + nájezdy.</t>
         </is>
       </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0002</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -16696,6 +16615,11 @@
           <t>I.ČNHL (2 sk. → finálová sk. + 2× o udržení) + I.SNHL (12). Kval o I.ligu.</t>
         </is>
       </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -16738,6 +16662,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0004</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -16780,6 +16709,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0005</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -16822,6 +16756,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0006</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -16864,6 +16803,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0007</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -16906,6 +16850,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0008</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -16948,6 +16897,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0009</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -16990,6 +16944,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0010</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -17032,6 +16991,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0011</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -17074,6 +17038,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0012</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -17116,6 +17085,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0013</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -17158,6 +17132,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0014</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -17205,6 +17184,11 @@
           <t>Kvalifikace vítězů krajských přeborů o ČNHL.</t>
         </is>
       </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0015</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -17247,6 +17231,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0016</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -17289,6 +17278,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0017</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -17336,6 +17330,11 @@
           <t>Kvalifikace o SNHL. Ze společného přeboru Západoslovenského kraje a Bratislavy postupuje nejlepší západoslovenský i bratislavský tým.</t>
         </is>
       </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0018</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -17378,6 +17377,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0019</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -17504,6 +17508,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0022</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -17630,6 +17639,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0025</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -17672,6 +17686,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0026</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -17714,6 +17733,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0028</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -17756,6 +17780,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0029</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -17887,6 +17916,11 @@
           <t>kvalifikace o KP I.třídy</t>
         </is>
       </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0032</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -17934,6 +17968,11 @@
           <t>Kvalifikace o II.třídu</t>
         </is>
       </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0033</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -18060,6 +18099,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0036</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -18102,6 +18146,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0037</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -18144,6 +18193,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0038</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -18186,6 +18240,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0039</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -18228,6 +18287,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0040</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -18270,6 +18334,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0044</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -18317,6 +18386,11 @@
           <t>kvalifikace o II.třídu</t>
         </is>
       </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0045</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -18359,6 +18433,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0046</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -18401,6 +18480,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0047</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -18569,6 +18653,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0048</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -18611,6 +18700,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0049</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -18653,6 +18747,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0050</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -18784,6 +18883,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0052</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -18826,6 +18930,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0053</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -18868,6 +18977,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0054</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -18910,6 +19024,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0055</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -18952,6 +19071,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0056</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -19078,6 +19202,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0059</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -19120,6 +19249,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0060</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -19162,6 +19296,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0061</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -19204,6 +19343,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L63" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0062</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -19246,6 +19390,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L64" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0063</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -19288,6 +19437,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L65" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0064</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -19330,6 +19484,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L66" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0065</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -19372,6 +19531,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L67" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0066</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -19419,6 +19583,11 @@
           <t>kvalifikace</t>
         </is>
       </c>
+      <c r="L68" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0067</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -19545,6 +19714,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L71" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0068</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -19587,6 +19761,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L72" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0069</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -19797,6 +19976,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L77" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0070</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -19839,6 +20023,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L78" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0071</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -20133,6 +20322,11 @@
           <t>Kontejner L30</t>
         </is>
       </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0083</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -20175,6 +20369,11 @@
           <t>Kontejner L40</t>
         </is>
       </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0084</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -20301,6 +20500,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0088</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -20343,6 +20547,11 @@
           <t>complete</t>
         </is>
       </c>
+      <c r="L90" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0089</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -20383,6 +20592,11 @@
       <c r="J91" t="inlineStr">
         <is>
           <t>complete</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>NODE_S1980_81_0090</t>
         </is>
       </c>
     </row>
@@ -22856,12 +23070,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň. || TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Doplnění „ZVIL" (Závody V.I. Lenina, dříve Škoda Plzeň, syn. Leninovy závody). Sjednocení s B-týmem (D21 striktně — složitější forma). || Doplnění „ZVIL" (Závody Vladimíra Iljiče Lenina, plzeňská Škoda po znárodnění). Sjednocení s B-týmem (D21 striktně — složitější forma). || Spartak ZVIL Plzeň 52/53 (10_liga). ZVIL = Závody V.I. Lenina (Leninovy závody, prejmenovane Skodovy zavody 1952). Plzeň = HC Škoda Plzeň (Wiki D42, viz ústava). Genealogie: Hokejový odbor SK Viktoria Plzeň (1929) -&gt; Sokol Plzeň IV (1948) -&gt; ZSJ Škodovy závody (1949) -&gt; ZSJ Leninovy závody / ZVIL (1952, prejmenování Škodovky na Leninovy závody) -&gt; Spartak Plzeň LZ / Spartak ZVIL (1953) -&gt; TJ Škoda Plzeň (1965) -&gt; HC Škoda Plzeň (1991) -&gt; HC Interconnex / ZKZ / Keramika / Lasselsberger / HC Plzeň 1929 / HC Škoda Plzeň (2012-dnes). Patterns: Škoda Viktoria Plzeň, Sokol Plzeň IV, ZSJ Škoda Plzeň, Spartak Plzeň, Spartak LZ Plzeň, Spartak ZVIL Plzeň, Škoda Plzeň, HC Škoda Plzeň. ZVIL = Závody V.I. Lenina = Leninovy závody (starší zkratka). LZ = Leninovy závody. city Plzeň. POZOR: 'ZSJ Škoda Hradec Králové' je JINÝ klub (Hradec Králové), Škodovy závody mely vice pobocek! || Plzeň = HC Škoda Plzeň (Wiki D42 - registr ustavy 04/2026). Velka metropole - vice paralelnich klubu. HLAVNI chain: Plzen 1929 (LTC Plzen) -&gt; Sokol -&gt; ZSJ Skoda -&gt; Spartak Skoda Plzen -&gt; TJ Skoda Plzen -&gt; HC Plzen -&gt; HC Skoda Plzen. DA Plzen = Doprava arm (paralelni vojensky). SPZ Plzen uc.15 = ucitelsky obvod. Sokol Plzen V (V = paty obvod). city Plzeň.</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Plzeň</t>
         </is>
       </c>
     </row>
@@ -23711,12 +23925,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov. || TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Železárny Prostějov B 61/62 (30_Jihomoravský, B-tym). Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - screenshot Pavlovo 04/2026, OPRAVA puvodni 'odpadly z 60/61'!). Genealogie: 1913 SK Prostějov -&gt; 1945 ČSSZ Prostějov (ČSSZ = Československé stavební závody, POTVRZENO Pavlem) -&gt; 1953 DSO Tatran Prostějov -&gt; Slovan Prostějov (1956) -&gt; 1959 TJ Železárny Prostějov -&gt; 1969 TJ Prostějov -&gt; HKC Prostějov -&gt; BSH Prostějov -&gt; 1989 IHC Prostějov (Ice Hockey Club) -&gt; LHK Jestřábi Prostějov (dnes). POZN: Klub NIKDY NEZANIKL - Pavlovo upresneni 04/2026: 1961/62 sestup z 2.ligy do krajskeho (kolega zapsal jen 'Prostějov' bez prefixu - patri do hlavni linie Železárny chain). city Prostějov. || Prostějov = LHK Jestřábi Prostějov / IHC Prostějov (Wiki D42 - registr ustavy 04/2026). Vsechny prostejovske chains. Hlavni: SK Prostějov (1913) -&gt; Sokol -&gt; ZSJ ČSSZ (Československe stavebni zavody) -&gt; Spartak Tatran Prostějov -&gt; LHK Jestrabi. city Prostějov.</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>Hradec Králové</t>
+          <t>Prostějov</t>
         </is>
       </c>
     </row>
@@ -23968,12 +24182,12 @@
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov. || TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>VTŽ Chomutov = Piráti Chomutov (Wiki D42 - registr ustavy 04/2026). VTŽ = Valcovny trub a zelezarny (NE Trinec). city Chomutov.</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>Mladá Boleslav</t>
+          <t>Chomutov</t>
         </is>
       </c>
     </row>
@@ -24099,12 +24313,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica. || TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Banská Bystrica = HC 05 Banská Bystrica (Wiki D42 - registr ustavy 04/2026). Slovensky kraj. Genealogie: Sokol NV (Národný výbor) -&gt; DSO Slovan -&gt; TJ Slovan Banska Bystrica -&gt; HC 05 Banská Bystrica. city Banská Bystrica.</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>ČSA Karviná</t>
+          <t>Banská Bystrica</t>
         </is>
       </c>
     </row>
@@ -24277,12 +24491,12 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec. || TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Liberec = VTJ Dukla Liberec (Wiki D42 - registr ustavy 04/2026). Vojensky klub. Konec 7/1978 (presun do Pisku). city Liberec.</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>Banská Bystrica</t>
+          <t>Liberec</t>
         </is>
       </c>
     </row>
@@ -28871,12 +29085,12 @@
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach] || TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Veselí nad Moravou = TJ Lokomotiva Veselí nad Moravou (Wiki D42 - registr ustavy 04/2026). Jihomoravsky kraj (okres Hodonín). Železničárský klub. NE Veselí nad Lužnicí (Jihocesky). city Veselí nad Moravou. || TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="J147" t="inlineStr">
         <is>
-          <t>Veselí nad Lužnicí</t>
+          <t>Veselí nad Moravou</t>
         </is>
       </c>
     </row>
@@ -39379,12 +39593,12 @@
       </c>
       <c r="I381" t="inlineStr">
         <is>
-          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava. || TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Dukla Jihlava (Wiki D42 - registr ustavy 04/2026). Vojensky armadni klub. city Jihlava.</t>
         </is>
       </c>
       <c r="J381" t="inlineStr">
         <is>
-          <t>Modeta Jihlava</t>
+          <t>Jihlava</t>
         </is>
       </c>
     </row>
@@ -42204,12 +42418,12 @@
       </c>
       <c r="I446" t="inlineStr">
         <is>
-          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice. || TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>Velké Popovice (Wiki - registr ustavy 04/2026). Stredocesky kraj. Hokejovy klub Slavoj Velké Popovice (HC Slavoj Velké Popovice). Patterns: Sokol Velke Popovice, Slavoj. city Velké Popovice.</t>
         </is>
       </c>
       <c r="J446" t="inlineStr">
         <is>
-          <t>Horní Benešov</t>
+          <t>Velké Popovice</t>
         </is>
       </c>
     </row>
@@ -50198,7 +50412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F50"/>
+  <dimension ref="A1:F42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -50252,12 +50466,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0006</t>
+          <t>CLUB_S1981_82_0014</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Plzeň' → 'České Budějovice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50272,12 +50486,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0014</t>
+          <t>CLUB_S1981_82_0016</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50292,12 +50506,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0016</t>
+          <t>CLUB_S1981_82_0022</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50312,12 +50526,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0022</t>
+          <t>CLUB_S1981_82_0030</t>
         </is>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50332,12 +50546,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0026</t>
+          <t>CLUB_S1981_82_0031</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Prostějov' → 'Hradec Králové' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50352,12 +50566,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0030</t>
+          <t>CLUB_S1981_82_0041</t>
         </is>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50372,12 +50586,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0031</t>
+          <t>CLUB_S1981_82_0045</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50392,12 +50606,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0032</t>
+          <t>CLUB_S1981_82_0053</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Chomutov' → 'Mladá Boleslav' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50412,12 +50626,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0035</t>
+          <t>CLUB_S1981_82_0068</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Banská Bystrica' → 'ČSA Karviná' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50432,12 +50646,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0039</t>
+          <t>CLUB_S1981_82_0068</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Kolora Liberec' → 'Banská Bystrica' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50452,12 +50666,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0041</t>
+          <t>CLUB_S1981_82_0074</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50472,12 +50686,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0045</t>
+          <t>CLUB_S1981_82_0076</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50492,12 +50706,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0053</t>
+          <t>CLUB_S1981_82_0110</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50512,12 +50726,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0068</t>
+          <t>CLUB_S1981_82_0141</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50532,12 +50746,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0068</t>
+          <t>CLUB_S1981_82_0142</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50552,12 +50766,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0074</t>
+          <t>CLUB_S1981_82_0145</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50572,12 +50786,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0076</t>
+          <t>CLUB_S1981_82_0151</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50592,12 +50806,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0110</t>
+          <t>CLUB_S1981_82_0153</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50612,12 +50826,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0141</t>
+          <t>CLUB_S1981_82_0166</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50632,12 +50846,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0142</t>
+          <t>CLUB_S1981_82_0175</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50652,12 +50866,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0145</t>
+          <t>CLUB_S1981_82_0187</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
     </row>
@@ -50672,12 +50886,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0151</t>
+          <t>CLUB_S1981_82_0213</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: auto-prev_club_id doplnění → CLUB_S1980_81_0206 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
     </row>
@@ -50692,12 +50906,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0153</t>
+          <t>CLUB_S1981_82_0230</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50712,12 +50926,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0153</t>
+          <t>CLUB_S1981_82_0234</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Veselí nad Moravou' → 'Veselí nad Lužnicí' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50732,12 +50946,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0166</t>
+          <t>CLUB_S1981_82_0256</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50752,12 +50966,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0175</t>
+          <t>CLUB_S1981_82_0269</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -50772,12 +50986,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0187</t>
+          <t>CLUB_S1981_82_0278</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50792,12 +51006,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0213</t>
+          <t>CLUB_S1981_82_0281</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: auto-prev_club_id doplnění → CLUB_S1980_81_0206 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50812,12 +51026,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0230</t>
+          <t>CLUB_S1981_82_0290</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -50832,12 +51046,12 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0234</t>
+          <t>CLUB_S1981_82_0294</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -50852,12 +51066,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0256</t>
+          <t>CLUB_S1981_82_0297</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50872,12 +51086,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0269</t>
+          <t>CLUB_S1981_82_0308</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50892,12 +51106,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0278</t>
+          <t>CLUB_S1981_82_0310</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -50912,12 +51126,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0281</t>
+          <t>CLUB_S1981_82_0339</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50932,12 +51146,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0290</t>
+          <t>CLUB_S1981_82_0340</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50952,12 +51166,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0294</t>
+          <t>CLUB_S1981_82_0349</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50972,12 +51186,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0297</t>
+          <t>CLUB_S1981_82_0385</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -50992,12 +51206,12 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0308</t>
+          <t>CLUB_S1981_82_0416</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -51012,12 +51226,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0310</t>
+          <t>CLUB_S1981_82_0419</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -51032,12 +51246,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0339</t>
+          <t>CLUB_S1981_82_0465</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51052,177 +51266,17 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0340</t>
+          <t>CLUB_S1981_82_0470</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>42</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>CLUB_S1981_82_0349</t>
-        </is>
-      </c>
-      <c r="D43" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>CLUB_S1981_82_0385</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>CLUB_S1981_82_0390</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Olomouc' → 'Modeta Jihlava' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CLUB_S1981_82_0416</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>CLUB_S1981_82_0419</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>CLUB_S1981_82_0456</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Voděrady' → 'Horní Benešov' (odvozeno z názvu klubu) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>CLUB_S1981_82_0465</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>prev_club_id / identita</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>CLUB_S1981_82_0470</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
           <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F50"/>
+  <autoFilter ref="A1:F42"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$42</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15860,7 +15860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D43"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15908,21 +15908,26 @@
       </c>
     </row>
     <row r="3">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>30ZAPC</t>
+        </is>
+      </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[club-fate] Viktoria Mariánské Lázně odstoupila po ZČ (club_id: CLUB_S1981_82_0215)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>TODO-auto</t>
+          <t>club-note-extracted</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="C4" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'NV Ústí nad Labem' → 'Ústí nad Labem' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -15934,7 +15939,7 @@
     <row r="5">
       <c r="C5" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'DP I. ČLTK Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -15946,7 +15951,7 @@
     <row r="6">
       <c r="C6" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Uhelné sklady Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15958,7 +15963,7 @@
     <row r="7">
       <c r="C7" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'TŽ VŘSR Třinec' → 'Třinec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -15970,7 +15975,7 @@
     <row r="8">
       <c r="C8" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žďas Žďár nad Sázavou' → 'Žďár nad Sázavou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -15982,7 +15987,7 @@
     <row r="9">
       <c r="C9" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SMZ Dubnica nad Váhom' → 'Dubnica nad Váhom' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -15994,7 +15999,7 @@
     <row r="10">
       <c r="C10" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Spišská Nová Ves' → 'Nová Ves' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -16006,7 +16011,7 @@
     <row r="11">
       <c r="C11" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'VVŠ PV Vyškov' → 'Vyškov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -16018,7 +16023,7 @@
     <row r="12">
       <c r="C12" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Rudá Hvězda Žižkov' → 'Žižkov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -16030,7 +16035,7 @@
     <row r="13">
       <c r="C13" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Žižkov' → 'Rudá Hvězda' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -16042,7 +16047,7 @@
     <row r="14">
       <c r="C14" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'UDPM JF Praha' → 'Praha' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -16054,7 +16059,7 @@
     <row r="15">
       <c r="C15" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Černice' → 'Horní Počernice' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -16090,7 +16095,7 @@
     <row r="18">
       <c r="C18" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'KŽ Králův Dvůr' → 'Králův Dvůr' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -16102,7 +16107,7 @@
     <row r="19">
       <c r="C19" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -16114,7 +16119,7 @@
     <row r="20">
       <c r="C20" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Hluboká' → 'Hluboká nad Vltavou' (odvozeno z názvu klubu) [polish_almanach]</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -16126,7 +16131,7 @@
     <row r="21">
       <c r="C21" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva  Veselí nad Moravou' → 'Veselí nad Moravou' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -16138,7 +16143,7 @@
     <row r="22">
       <c r="C22" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Smrčina Horní Planá' → 'Planá' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -16150,7 +16155,7 @@
     <row r="23">
       <c r="C23" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Vajgar Jindřichův Hradec' → 'Jindřichův Hradec' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -16162,7 +16167,7 @@
     <row r="24">
       <c r="C24" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1980_81_0206 (weak, jméno+město; verifikovat) [fix_continuity]</t>
+          <t>[TBD] prev_club_id / identita: TBD-IDENTITY: vyžaduje verifikaci primárním zdrojem. (D28 — pomalý nástup éry Slavoj/Spartak v 51/52.)</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -16174,7 +16179,7 @@
     <row r="25">
       <c r="C25" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: auto-prev_club_id doplnění → CLUB_S1980_81_0206 (weak, jméno+město; verifikovat) [fix_continuity]</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -16186,7 +16191,7 @@
     <row r="26">
       <c r="C26" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: extrahováno z block_name: 'Viktoria Mariánské Lázně odstoupila po ZČ' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -16198,7 +16203,7 @@
     <row r="27">
       <c r="C27" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -16210,7 +16215,7 @@
     <row r="28">
       <c r="C28" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -16222,7 +16227,7 @@
     <row r="29">
       <c r="C29" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -16234,7 +16239,7 @@
     <row r="30">
       <c r="C30" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -16246,7 +16251,7 @@
     <row r="31">
       <c r="C31" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -16258,7 +16263,7 @@
     <row r="32">
       <c r="C32" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -16270,7 +16275,7 @@
     <row r="33">
       <c r="C33" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -16282,7 +16287,7 @@
     <row r="34">
       <c r="C34" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -16294,7 +16299,7 @@
     <row r="35">
       <c r="C35" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -16306,7 +16311,7 @@
     <row r="36">
       <c r="C36" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -16318,7 +16323,7 @@
     <row r="37">
       <c r="C37" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -16330,7 +16335,7 @@
     <row r="38">
       <c r="C38" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -16342,7 +16347,7 @@
     <row r="39">
       <c r="C39" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -16354,7 +16359,7 @@
     <row r="40">
       <c r="C40" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -16366,7 +16371,7 @@
     <row r="41">
       <c r="C41" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -16378,7 +16383,7 @@
     <row r="42">
       <c r="C42" t="inlineStr">
         <is>
-          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>[TBD] prev_club_id / identita: TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -16390,10 +16395,34 @@
     <row r="43">
       <c r="C43" t="inlineStr">
         <is>
+          <t>[TBD] prev_club_id / identita: TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>[TBD] prev_club_id / identita: TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="C45" t="inlineStr">
+        <is>
           <t>[TBD] prev_club_id / identita: TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr">
+      <c r="D45" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -31929,7 +31958,7 @@
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>Mariánské Lázně (Wiki - registr ustavy 04/2026). Zapadocesky/Karlovarsky kraj. - hokej tradice mensi. city Mariánské Lázně.</t>
+          <t>Mariánské Lázně (Wiki - registr ustavy 04/2026). Zapadocesky/Karlovarsky kraj. - hokej tradice mensi. city Mariánské Lázně. || TBD: extrahováno z block_name: 'Viktoria Mariánské Lázně odstoupila po ZČ' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
@@ -50412,7 +50441,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F42"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -50906,12 +50935,12 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0230</t>
+          <t>CLUB_S1981_82_0215</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: extrahováno z block_name: 'Viktoria Mariánské Lázně odstoupila po ZČ' [fix_club_notes_in_block_name]</t>
         </is>
       </c>
     </row>
@@ -50926,12 +50955,12 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0234</t>
+          <t>CLUB_S1981_82_0230</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Start VD Luby' → 'Luby' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50946,12 +50975,12 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0256</t>
+          <t>CLUB_S1981_82_0234</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Lokomotiva depo Cheb' → 'Cheb' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50966,12 +50995,12 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0269</t>
+          <t>CLUB_S1981_82_0256</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
+          <t>TBD: city 'Technické služby Děčín' → 'Děčín' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -50986,12 +51015,12 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0278</t>
+          <t>CLUB_S1981_82_0269</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Ústecký Sokol Louky — neznámá obec, district „skupina B" neuvádí lokalitu. city dočasně „Louky (UNL)" do vyřešení. prev na 51/52 0427 (Karviná) zachován jako stopa, ale je to chybně — k vyřešení v Todo.</t>
         </is>
       </c>
     </row>
@@ -51006,12 +51035,12 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0281</t>
+          <t>CLUB_S1981_82_0278</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Důl Jana Žižky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51026,12 +51055,12 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0290</t>
+          <t>CLUB_S1981_82_0281</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
+          <t>TBD: city 'SSM Statky Chomutov' → 'Chomutov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51046,7 +51075,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0294</t>
+          <t>CLUB_S1981_82_0290</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
@@ -51066,12 +51095,12 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0297</t>
+          <t>CLUB_S1981_82_0294</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: Klub „Jaroměř" bez prefixu, level okresní. Prev na 49/50 0670 (Stadion Jaroměř) odebrán — to je jiný klub. K ověření: zda je to nově vzniklý klub nebo navazuje na nějakou jinou jaroměřskou organizaci.</t>
         </is>
       </c>
     </row>
@@ -51086,12 +51115,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0308</t>
+          <t>CLUB_S1981_82_0297</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Tepna ČKD Hronov' → 'Hronov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51106,12 +51135,12 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0310</t>
+          <t>CLUB_S1981_82_0308</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
+          <t>TBD: city 'OSP Nový Bydžov' → 'Nový Bydžov' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51126,12 +51155,12 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0339</t>
+          <t>CLUB_S1981_82_0310</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0902 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0841 „Moravská Třebová" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Alternativa: hokej v MT mohl tehdy teprve vznikat → mohl by být bez prev. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -51146,12 +51175,12 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0340</t>
+          <t>CLUB_S1981_82_0339</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'SSM SNV Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51166,12 +51195,12 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0349</t>
+          <t>CLUB_S1981_82_0340</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: city 'Povodí Labe Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51186,12 +51215,12 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0385</t>
+          <t>CLUB_S1981_82_0349</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
+          <t>TBD: city 'Dopravní podnik Pardubice' → 'Pardubice' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
@@ -51206,7 +51235,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0416</t>
+          <t>CLUB_S1981_82_0385</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
@@ -51226,12 +51255,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0419</t>
+          <t>CLUB_S1981_82_0416</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
+          <t>TBD: prev_club_id v almanachu ukazoval na neexistující CLUB_S1949_50_0906 (mezera v číslování 49/50). Smart fix: napojeno na CLUB_S1949_50_0812 „Vyškov" (30_Brněnský, L50) — jediný kandidát se shodným clean_name + regionem. Možný přesun mezi regiony nebo sestup z L50 na okresní úroveň. K ověření Pavlem.</t>
         </is>
       </c>
     </row>
@@ -51246,12 +51275,12 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>CLUB_S1981_82_0465</t>
+          <t>CLUB_S1981_82_0419</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+          <t>TBD: clean = "(Třešť) – (Dačice)" - format meziokresni soutez nejasny. K vyjasneni Pavlem (D40). Almanach komentar ponechan.</t>
         </is>
       </c>
     </row>
@@ -51266,17 +51295,37 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
+          <t>CLUB_S1981_82_0465</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>TBD: city 'Důl Prezident Gottwald Horní Suchá' → 'Horní Suchá' (oříznut firemní prefix) [polish_almanach]</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>prev_club_id / identita</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
           <t>CLUB_S1981_82_0470</t>
         </is>
       </c>
-      <c r="D42" s="6" t="inlineStr">
+      <c r="D43" s="6" t="inlineStr">
         <is>
           <t>TBD: city 'Sigma ZTS Olomouc' → 'Olomouc' (oříznut firemní prefix) [polish_almanach]</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F42"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -64539,7 +64588,7 @@
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Krajský přebor / O 5.-7.místo / Viktoria Mariánské Lázně odstoupila po ZČ</t>
+          <t>Krajský přebor / O 5.-7.místo</t>
         </is>
       </c>
       <c r="C18" s="2" t="n"/>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$55</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -15860,7 +15860,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D45"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16423,6 +16423,150 @@
         </is>
       </c>
       <c r="D45" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>TODO-auto</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -50441,7 +50585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -51324,8 +51468,248 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Poldi SONP Kladno</t>
+        </is>
+      </c>
+      <c r="D45" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>CHZ Litvínov</t>
+        </is>
+      </c>
+      <c r="D46" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>TJ Vítkovice</t>
+        </is>
+      </c>
+      <c r="D47" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Tesla Pardubice</t>
+        </is>
+      </c>
+      <c r="D48" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Motor České Budějovice</t>
+        </is>
+      </c>
+      <c r="D49" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Sparta Praha</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>VSŽ Košice</t>
+        </is>
+      </c>
+      <c r="D51" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>TJ Gottwaldov</t>
+        </is>
+      </c>
+      <c r="D52" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Zetor Brno</t>
+        </is>
+      </c>
+      <c r="D53" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Škoda Plzeň</t>
+        </is>
+      </c>
+      <c r="D54" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>tabulka (re-extrakce)</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Dukla Trenčín</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:F43"/>
+  <autoFilter ref="A1:F55"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -29,7 +29,7 @@
     <sheet name="TODO" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$55</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="19" hidden="1">'TODO'!$A$1:$F$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -718,29 +718,27 @@
         <v>44</v>
       </c>
       <c r="G4" t="n">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="H4" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J4" t="n">
-        <v>4</v>
+        <v>179</v>
       </c>
       <c r="K4" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L4" t="n">
+        <v>89</v>
       </c>
       <c r="M4" t="n">
-        <v>89</v>
+        <v>74</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
@@ -806,29 +804,27 @@
         <v>44</v>
       </c>
       <c r="G5" t="n">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="H5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>174</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L5" t="n">
+        <v>134</v>
       </c>
       <c r="M5" t="n">
-        <v>134</v>
+        <v>62</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
@@ -894,29 +890,27 @@
         <v>44</v>
       </c>
       <c r="G6" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="H6" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I6" t="n">
-        <v>3</v>
+        <v>19</v>
       </c>
       <c r="J6" t="n">
-        <v>16</v>
+        <v>205</v>
       </c>
       <c r="K6" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L6" t="n">
+        <v>167</v>
       </c>
       <c r="M6" t="n">
-        <v>167</v>
+        <v>50</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
@@ -982,29 +976,27 @@
         <v>44</v>
       </c>
       <c r="G7" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="H7" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="I7" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J7" t="n">
-        <v>16</v>
+        <v>179</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L7" t="n">
+        <v>151</v>
       </c>
       <c r="M7" t="n">
-        <v>151</v>
+        <v>48</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
@@ -1070,29 +1062,27 @@
         <v>44</v>
       </c>
       <c r="G8" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="H8" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I8" t="n">
-        <v>1</v>
+        <v>24</v>
       </c>
       <c r="J8" t="n">
-        <v>23</v>
+        <v>183</v>
       </c>
       <c r="K8" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L8" t="n">
+        <v>169</v>
       </c>
       <c r="M8" t="n">
-        <v>169</v>
+        <v>40</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
@@ -1158,29 +1148,27 @@
         <v>44</v>
       </c>
       <c r="G9" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H9" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I9" t="n">
-        <v>5</v>
+        <v>24</v>
       </c>
       <c r="J9" t="n">
-        <v>19</v>
+        <v>145</v>
       </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L9" t="n">
+        <v>145</v>
       </c>
       <c r="M9" t="n">
-        <v>145</v>
+        <v>40</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
@@ -1246,29 +1234,27 @@
         <v>44</v>
       </c>
       <c r="G10" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="H10" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="I10" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
       <c r="J10" t="n">
-        <v>21</v>
+        <v>129</v>
       </c>
       <c r="K10" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L10" t="n">
+        <v>151</v>
       </c>
       <c r="M10" t="n">
-        <v>151</v>
+        <v>40</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
@@ -1334,29 +1320,27 @@
         <v>44</v>
       </c>
       <c r="G11" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H11" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I11" t="n">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="J11" t="n">
-        <v>22</v>
+        <v>150</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L11" t="n">
+        <v>197</v>
       </c>
       <c r="M11" t="n">
-        <v>197</v>
+        <v>40</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1422,29 +1406,27 @@
         <v>44</v>
       </c>
       <c r="G12" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I12" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
       <c r="J12" t="n">
-        <v>22</v>
+        <v>119</v>
       </c>
       <c r="K12" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L12" t="n">
+        <v>135</v>
       </c>
       <c r="M12" t="n">
-        <v>135</v>
+        <v>34</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1515,29 +1497,27 @@
         <v>44</v>
       </c>
       <c r="G13" t="n">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="H13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
-        <v>1</v>
+        <v>27</v>
       </c>
       <c r="J13" t="n">
-        <v>26</v>
+        <v>123</v>
       </c>
       <c r="K13" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L13" t="n">
+        <v>174</v>
       </c>
       <c r="M13" t="n">
-        <v>174</v>
+        <v>34</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1603,29 +1583,27 @@
         <v>44</v>
       </c>
       <c r="G14" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="H14" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I14" t="n">
-        <v>3</v>
+        <v>27</v>
       </c>
       <c r="J14" t="n">
-        <v>24</v>
+        <v>128</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L14" t="n">
+        <v>181</v>
       </c>
       <c r="M14" t="n">
-        <v>181</v>
+        <v>34</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1691,29 +1669,27 @@
         <v>44</v>
       </c>
       <c r="G15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="J15" t="n">
-        <v>23</v>
+        <v>133</v>
       </c>
       <c r="K15" t="inlineStr">
         <is>
           <t>:</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>:</t>
-        </is>
+      <c r="L15" t="n">
+        <v>154</v>
       </c>
       <c r="M15" t="n">
-        <v>154</v>
+        <v>32</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -15860,7 +15836,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D57"/>
+  <dimension ref="A1:D45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16423,150 +16399,6 @@
         </is>
       </c>
       <c r="D45" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>TODO-auto</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>[TBD] tabulka (re-extrakce): chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
         <is>
           <t>TODO-auto</t>
         </is>
@@ -50585,7 +50417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -51468,248 +51300,8 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>43</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Dukla Jihlava</t>
-        </is>
-      </c>
-      <c r="D44" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>44</v>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Poldi SONP Kladno</t>
-        </is>
-      </c>
-      <c r="D45" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>CHZ Litvínov</t>
-        </is>
-      </c>
-      <c r="D46" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>TJ Vítkovice</t>
-        </is>
-      </c>
-      <c r="D47" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>47</v>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Tesla Pardubice</t>
-        </is>
-      </c>
-      <c r="D48" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>48</v>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Motor České Budějovice</t>
-        </is>
-      </c>
-      <c r="D49" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="n">
-        <v>49</v>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Sparta Praha</t>
-        </is>
-      </c>
-      <c r="D50" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>VSŽ Košice</t>
-        </is>
-      </c>
-      <c r="D51" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>TJ Gottwaldov</t>
-        </is>
-      </c>
-      <c r="D52" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Zetor Brno</t>
-        </is>
-      </c>
-      <c r="D53" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Škoda Plzeň</t>
-        </is>
-      </c>
-      <c r="D54" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>tabulka (re-extrakce)</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Dukla Trenčín</t>
-        </is>
-      </c>
-      <c r="D55" s="6" t="inlineStr">
-        <is>
-          <t>chybí obdržené branky (GA) — doplnit ze zdroje</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:F55"/>
+  <autoFilter ref="A1:F43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -46503,7 +46503,7 @@
         <v>5</v>
       </c>
       <c r="J17" t="n">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="K17" t="inlineStr">
         <is>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -16415,7 +16415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L102"/>
+  <dimension ref="A1:N102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -16477,6 +16477,16 @@
       <c r="L1" t="inlineStr">
         <is>
           <t>prev_node_id</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>entry</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>phase_order</t>
         </is>
       </c>
     </row>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -16761,6 +16761,16 @@
           <t>NODE_S1981_82_0001</t>
         </is>
       </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0007</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0008</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16775,6 +16785,14 @@
         <is>
           <t>NODE_S1980_81_0006</t>
         </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -16808,6 +16826,8 @@
           <t>NODE_S1981_82_0001</t>
         </is>
       </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16822,6 +16842,14 @@
         <is>
           <t>NODE_S1980_81_0007</t>
         </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N8" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -16855,6 +16883,8 @@
           <t>NODE_S1981_82_0001</t>
         </is>
       </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16869,6 +16899,14 @@
         <is>
           <t>NODE_S1980_81_0008</t>
         </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N9" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="10">
@@ -17043,6 +17081,8 @@
           <t>NODE_S1981_82_0004</t>
         </is>
       </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17057,6 +17097,14 @@
         <is>
           <t>NODE_S1980_81_0012</t>
         </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
@@ -17090,6 +17138,8 @@
           <t>NODE_S1981_82_0004</t>
         </is>
       </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17104,6 +17154,14 @@
         <is>
           <t>NODE_S1980_81_0013</t>
         </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>dolní část ZČ</t>
+        </is>
+      </c>
+      <c r="N14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -17137,6 +17195,12 @@
           <t>NODE_S1981_82_0005</t>
         </is>
       </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0012</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17151,6 +17215,14 @@
         <is>
           <t>NODE_S1980_81_0014</t>
         </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -17513,6 +17585,16 @@
           <t>NODE_S1981_82_0019</t>
         </is>
       </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0023</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0024</t>
+        </is>
+      </c>
       <c r="I23" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17527,6 +17609,14 @@
         <is>
           <t>NODE_S1980_81_0022</t>
         </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -17560,6 +17650,8 @@
           <t>NODE_S1981_82_0019</t>
         </is>
       </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17569,6 +17661,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N24" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="25">
@@ -17602,6 +17702,8 @@
           <t>NODE_S1981_82_0019</t>
         </is>
       </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17611,6 +17713,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>5.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N25" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="26">
@@ -17639,6 +17749,12 @@
           <t>REG_STC</t>
         </is>
       </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0027</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17658,6 +17774,14 @@
         <is>
           <t>NODE_S1980_81_0025</t>
         </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>9 týmů</t>
+        </is>
+      </c>
+      <c r="N26" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="27">
@@ -17738,6 +17862,8 @@
           <t>NODE_S1981_82_0025</t>
         </is>
       </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17752,6 +17878,14 @@
         <is>
           <t>NODE_S1980_81_0028</t>
         </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -18104,6 +18238,8 @@
           <t>NODE_S1981_82_0025</t>
         </is>
       </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18118,6 +18254,14 @@
         <is>
           <t>NODE_S1980_81_0036</t>
         </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N36" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="37">
@@ -18532,6 +18676,12 @@
           <t>NODE_S1981_82_0042</t>
         </is>
       </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0045</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18541,6 +18691,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>7 týmů</t>
+        </is>
+      </c>
+      <c r="N45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -18574,6 +18732,8 @@
           <t>NODE_S1981_82_0042</t>
         </is>
       </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18583,6 +18743,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N46" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="47">
@@ -18616,6 +18784,8 @@
           <t>NODE_S1981_82_0042</t>
         </is>
       </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18625,6 +18795,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N47" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="48">
@@ -18982,6 +19160,12 @@
           <t>NODE_S1981_82_0052</t>
         </is>
       </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0057</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18996,6 +19180,14 @@
         <is>
           <t>NODE_S1980_81_0054</t>
         </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -19123,6 +19315,8 @@
           <t>NODE_S1981_82_0052</t>
         </is>
       </c>
+      <c r="G58" t="inlineStr"/>
+      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19132,6 +19326,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="59">
@@ -19165,6 +19367,8 @@
           <t>NODE_S1981_82_0052</t>
         </is>
       </c>
+      <c r="G59" t="inlineStr"/>
+      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19174,6 +19378,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="60">
@@ -19348,6 +19560,16 @@
           <t>NODE_S1981_82_0060</t>
         </is>
       </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0068</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0064</t>
+        </is>
+      </c>
       <c r="I63" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19362,6 +19584,14 @@
         <is>
           <t>NODE_S1980_81_0062</t>
         </is>
+      </c>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>8 týmů</t>
+        </is>
+      </c>
+      <c r="N63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -19395,6 +19625,8 @@
           <t>NODE_S1981_82_0060</t>
         </is>
       </c>
+      <c r="G64" t="inlineStr"/>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19409,6 +19641,14 @@
         <is>
           <t>NODE_S1980_81_0063</t>
         </is>
+      </c>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N64" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="65">
@@ -19442,6 +19682,8 @@
           <t>NODE_S1981_82_0060</t>
         </is>
       </c>
+      <c r="G65" t="inlineStr"/>
+      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19456,6 +19698,14 @@
         <is>
           <t>NODE_S1980_81_0064</t>
         </is>
+      </c>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>6.–8. ZČ</t>
+        </is>
+      </c>
+      <c r="N65" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="66">
@@ -19635,6 +19885,12 @@
           <t>NODE_S1981_82_0060</t>
         </is>
       </c>
+      <c r="G69" t="inlineStr"/>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0064</t>
+        </is>
+      </c>
       <c r="I69" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19644,6 +19900,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>střed tabulky ZČ</t>
+        </is>
+      </c>
+      <c r="N69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -19813,6 +20077,12 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0073</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19822,6 +20092,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>12 týmů</t>
+        </is>
+      </c>
+      <c r="N73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -19855,6 +20133,8 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
+      <c r="G74" t="inlineStr"/>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19864,6 +20144,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N74" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="75">
@@ -19897,6 +20185,8 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
+      <c r="G75" t="inlineStr"/>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19906,6 +20196,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -20117,6 +20415,8 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
+      <c r="G80" t="inlineStr"/>
+      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20126,6 +20426,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N80" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="81">
@@ -20201,6 +20509,8 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
+      <c r="G82" t="inlineStr"/>
+      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20210,6 +20520,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M82" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N82" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="83">
@@ -20243,6 +20561,8 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
+      <c r="G83" t="inlineStr"/>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20252,6 +20572,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M83" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N83" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -20285,6 +20613,8 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
+      <c r="G84" t="inlineStr"/>
+      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20294,6 +20624,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>poražení play-off</t>
+        </is>
+      </c>
+      <c r="N84" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="85">
@@ -20322,6 +20660,12 @@
           <t>REG_SVM</t>
         </is>
       </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>NODE_S1981_82_0086</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20341,6 +20685,14 @@
         <is>
           <t>NODE_S1980_81_0083</t>
         </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>10 týmů</t>
+        </is>
+      </c>
+      <c r="N85" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="86">
@@ -20421,6 +20773,8 @@
           <t>NODE_S1981_82_0084</t>
         </is>
       </c>
+      <c r="G87" t="inlineStr"/>
+      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20430,6 +20784,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M87" t="inlineStr">
+        <is>
+          <t>vítězové SF</t>
+        </is>
+      </c>
+      <c r="N87" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="88">
@@ -20463,6 +20825,8 @@
           <t>NODE_S1981_82_0084</t>
         </is>
       </c>
+      <c r="G88" t="inlineStr"/>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20472,6 +20836,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M88" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (dolní)</t>
+        </is>
+      </c>
+      <c r="N88" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="89">
@@ -21034,6 +21406,8 @@
           <t>NODE_S1981_82_0099</t>
         </is>
       </c>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21043,6 +21417,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>účastníci soutěže</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="102">
@@ -21076,6 +21458,8 @@
           <t>NODE_S1981_82_0099</t>
         </is>
       </c>
+      <c r="G102" t="inlineStr"/>
+      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21085,6 +21469,14 @@
         <is>
           <t>complete</t>
         </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>sk. o 5.–8. (horní)</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -714,6 +714,11 @@
           <t>Dukla Jihlava</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>M</t>
+        </is>
+      </c>
       <c r="F4" t="n">
         <v>44</v>
       </c>
@@ -16826,8 +16831,6 @@
           <t>NODE_S1981_82_0001</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -16883,8 +16886,6 @@
           <t>NODE_S1981_82_0001</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17081,8 +17082,6 @@
           <t>NODE_S1981_82_0004</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
       <c r="I13" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17138,8 +17137,6 @@
           <t>NODE_S1981_82_0004</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17195,7 +17192,6 @@
           <t>NODE_S1981_82_0005</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
           <t>NODE_S1981_82_0012</t>
@@ -17650,8 +17646,6 @@
           <t>NODE_S1981_82_0019</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17702,8 +17696,6 @@
           <t>NODE_S1981_82_0019</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17754,7 +17746,6 @@
           <t>NODE_S1981_82_0027</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
       <c r="I26" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -17862,8 +17853,6 @@
           <t>NODE_S1981_82_0025</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
       <c r="I28" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18238,8 +18227,6 @@
           <t>NODE_S1981_82_0025</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
       <c r="I36" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18681,7 +18668,6 @@
           <t>NODE_S1981_82_0045</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
       <c r="I45" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18732,8 +18718,6 @@
           <t>NODE_S1981_82_0042</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -18784,8 +18768,6 @@
           <t>NODE_S1981_82_0042</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
       <c r="I47" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19165,7 +19147,6 @@
           <t>NODE_S1981_82_0057</t>
         </is>
       </c>
-      <c r="H55" t="inlineStr"/>
       <c r="I55" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19315,8 +19296,6 @@
           <t>NODE_S1981_82_0052</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr"/>
       <c r="I58" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19367,8 +19346,6 @@
           <t>NODE_S1981_82_0052</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr"/>
       <c r="I59" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19625,8 +19602,6 @@
           <t>NODE_S1981_82_0060</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr"/>
       <c r="I64" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19682,8 +19657,6 @@
           <t>NODE_S1981_82_0060</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr"/>
       <c r="I65" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -19885,7 +19858,6 @@
           <t>NODE_S1981_82_0060</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
           <t>NODE_S1981_82_0064</t>
@@ -20082,7 +20054,6 @@
           <t>NODE_S1981_82_0073</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
       <c r="I73" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20133,8 +20104,6 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20185,8 +20154,6 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr"/>
-      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20415,8 +20382,6 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr"/>
-      <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20509,8 +20474,6 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr"/>
-      <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20561,8 +20524,6 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr"/>
-      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20613,8 +20574,6 @@
           <t>NODE_S1981_82_0070</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr"/>
-      <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20665,7 +20624,6 @@
           <t>NODE_S1981_82_0086</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20773,8 +20731,6 @@
           <t>NODE_S1981_82_0084</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr"/>
-      <c r="H87" t="inlineStr"/>
       <c r="I87" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -20825,8 +20781,6 @@
           <t>NODE_S1981_82_0084</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr"/>
-      <c r="H88" t="inlineStr"/>
       <c r="I88" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21406,8 +21360,6 @@
           <t>NODE_S1981_82_0099</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr"/>
-      <c r="H101" t="inlineStr"/>
       <c r="I101" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -21458,8 +21410,6 @@
           <t>NODE_S1981_82_0099</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr"/>
-      <c r="H102" t="inlineStr"/>
       <c r="I102" t="inlineStr">
         <is>
           <t>2-1-0</t>
@@ -45020,7 +44970,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B53"/>
+  <dimension ref="A1:B54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -45656,6 +45606,18 @@
       <c r="B53" t="inlineStr">
         <is>
           <t>Slovenské krajské větve jsou na jednom listu, ale jsou paralelní, ne vertikální.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>mistr</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Dukla Jihlava</t>
         </is>
       </c>
     </row>

--- a/data/S1981_82_FINAL.xlsx
+++ b/data/S1981_82_FINAL.xlsx
@@ -46858,13 +46858,13 @@
         <v>22</v>
       </c>
       <c r="G17" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
         <v>3</v>
-      </c>
-      <c r="I17" t="n">
-        <v>5</v>
       </c>
       <c r="J17" t="n">
         <v>106</v>
@@ -46878,7 +46878,7 @@
         <v>61</v>
       </c>
       <c r="M17" t="n">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
